--- a/docs/xlsx/jobs-2026-10-04.xlsx
+++ b/docs/xlsx/jobs-2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
   <si>
     <t>Title</t>
   </si>
@@ -40,15 +40,69 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Coach Mentor-Fellow (Americorps Position)</t>
+  </si>
+  <si>
+    <t>Soccer Without Borders</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 40300.00 - 40300.00/year</t>
+  </si>
+  <si>
+    <t>Sports Recreation, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af3174e5f951437cbb52d5543e20688e-coach-mentor-fellow-americorps-position-soccer-without-borders-oakland</t>
+  </si>
+  <si>
+    <t>Development Manager (USA Preferred, or UK)</t>
+  </si>
+  <si>
+    <t>Project Slingshot</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26c73f43b76d4c23a63252a7a11c2d4a-development-manager-usa-preferred-or-uk-project-slingshot-dover</t>
+  </si>
+  <si>
+    <t>Digital Marketing Director (US Remote)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d8f7bb68ee141eead1465845d5ed432-digital-marketing-director-us-remote-project-slingshot-dover</t>
+  </si>
+  <si>
+    <t>Digital Marketing Manager (US Remote)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63c567a23083428bace9301a9b23f4b0-digital-marketing-manager-us-remote-project-slingshot-dover</t>
+  </si>
+  <si>
     <t>International Director</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Contract</t>
   </si>
   <si>
@@ -61,6 +115,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2037bd4fd1234d3db5097a363f7f17ca-international-director-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Program Coordinator, Project Coordinator, Project Manager, Program Manager. RATED DC's #1 BEST...</t>
+  </si>
+  <si>
+    <t>Global Language Network</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 43000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/505604c6ce164621b19ccbdc62d05e17-program-coordinator-project-coordinator-project-manager-program-manager-rated-dcs-1-best-global-language-network-washington</t>
+  </si>
+  <si>
     <t>Teaching Abroad Opportunity - Abaarso School (Somaliland)</t>
   </si>
   <si>
@@ -68,9 +140,6 @@
   </si>
   <si>
     <t>Hargeisa, Somaliland, Woqoyi Galbed, SO</t>
-  </si>
-  <si>
-    <t>Full Time</t>
   </si>
   <si>
     <t>USD 325.00 - 325.00/month</t>
@@ -561,7 +630,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -634,16 +703,131 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -651,6 +835,11 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-04.xlsx
+++ b/docs/xlsx/jobs-2026-10-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>Title</t>
   </si>
@@ -61,6 +61,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/af3174e5f951437cbb52d5543e20688e-coach-mentor-fellow-americorps-position-soccer-without-borders-oakland</t>
   </si>
   <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Inquilinos Unidos (United Tenants)</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 74000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fbdcbd15108479b9df85e0df12b738a-development-manager-inquilinos-unidos-united-tenants-los-angeles</t>
+  </si>
+  <si>
     <t>Development Manager (USA Preferred, or UK)</t>
   </si>
   <si>
@@ -115,6 +133,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2037bd4fd1234d3db5097a363f7f17ca-international-director-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Minnesota Environmental Justice Manager, Full Time Exempt (Remote)</t>
+  </si>
+  <si>
+    <t>Center for Earth, Energy and Democracy</t>
+  </si>
+  <si>
+    <t>Remote (Minnesota)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79dfd5e9752c479480bb57aeffcf538c-minnesota-environmental-justice-manager-full-time-exempt-remote-center-for-earth-energy-and-democracy-minneapolis</t>
+  </si>
+  <si>
     <t>Program Coordinator, Project Coordinator, Project Manager, Program Manager. RATED DC's #1 BEST...</t>
   </si>
   <si>
@@ -131,6 +167,39 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/505604c6ce164621b19ccbdc62d05e17-program-coordinator-project-coordinator-project-manager-program-manager-rated-dcs-1-best-global-language-network-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager, Grants &amp; Contracts</t>
+  </si>
+  <si>
+    <t>Coalition for Asian American Children and Families</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ca5fa295da64ae6836cd385bcf55994-senior-manager-grants-contracts-coalition-for-asian-american-children-and-families-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Legal Action Center (NYC, D.C.)</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f9e5bd76b3a447790f8d75218b88d69-staff-attorney-legal-action-center-nyc-dc-new-york</t>
   </si>
   <si>
     <t>Teaching Abroad Opportunity - Abaarso School (Somaliland)</t>
@@ -630,7 +699,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -720,65 +789,65 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>32</v>
@@ -792,10 +861,10 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
       </c>
       <c r="E7" t="s">
         <v>36</v>
@@ -828,6 +897,98 @@
       </c>
       <c r="H8" s="2" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -840,6 +1001,10 @@
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
     <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
